--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:15:17+00:00</t>
+    <t>2026-06-15T08:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:40:43+00:00</t>
+    <t>2026-06-15T08:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:59:58+00:00</t>
+    <t>2026-06-18T07:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,22 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Strukturiertes onkologisches Therapieziel auf Basis von `Goal`. Die Zielart wird über `category` codiert (Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme). Über die Extension `onko-therapy-intent` kann zusätzlich die Therapieintention der zugehörigen Behandlungslinie hinterlegt werden. Das Ziel referenziert über `addresses` die adressierte Tumorerkrankung und kann über `Goal.outcomeReference` an Verlaufs-Observations (z. B. mCODE CancerDiseaseStatus) gebunden werden.</t>
+    <t>Strukturiertes onkologisches Therapieziel auf Basis von `Goal`.
+Das Profil ist an den **HL7 FHIR US Multiple Chronic Conditions (MCC) eCare Plan**
+([MCCGoal](https://build.fhir.org/ig/HL7/fhir-us-mcc/StructureDefinition-MCCGoal.html))
+angelehnt: Das Therapieziel ist eine eigenständige, referenzbasierte Ressource, die über
+`addresses` mit den adressierten Erkrankungen und über `outcomeReference` mit beobachteten
+Ergebnissen (Verlaufs-Observations) verknüpft wird.
+Onkologiespezifische Ergänzungen gegenüber MCC:
+- Die Zielart wird über `category` aus `OnkoTherapyGoalTypeVS` codiert (Heilung,
+  Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme).
+- Über die Extension `onko-therapy-intent` kann zusätzlich die Therapieintention der
+  zugehörigen Behandlungslinie hinterlegt werden.
+- `outcomeReference` bindet das Ziel an Verlaufs-Observations (z. B. mCODE
+  CancerDiseaseStatus / Response Assessment), wodurch das Tumoransprechen auf das Ziel
+  bezogen ausgewertet werden kann.
+`achievementStatus` bildet — analog MCC — den Erreichungsgrad bzw. die Zielakzeptanz ab
+(z. B. erreicht, in Bearbeitung, nicht erreicht).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -2322,7 +2337,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2343,7 +2358,7 @@
         <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>76</v>
@@ -2772,7 +2787,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -2791,7 +2806,7 @@
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>76</v>
@@ -2990,7 +3005,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>185</v>
       </c>
@@ -3009,7 +3024,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>76</v>
@@ -3884,7 +3899,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>244</v>
       </c>
@@ -3903,7 +3918,7 @@
         <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>76</v>
@@ -3993,7 +4008,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>249</v>
       </c>
@@ -4012,7 +4027,7 @@
         <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>76</v>
@@ -4104,7 +4119,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>255</v>
       </c>
@@ -4123,7 +4138,7 @@
         <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>76</v>
@@ -4437,7 +4452,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>271</v>
       </c>
@@ -4456,7 +4471,7 @@
         <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>76</v>
@@ -4659,7 +4674,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>284</v>
       </c>
@@ -4678,7 +4693,7 @@
         <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>76</v>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T07:59:27+00:00</t>
+    <t>2026-06-18T08:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:58+00:00</t>
+    <t>2026-06-18T08:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2337,7 +2337,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>139</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>76</v>
@@ -2896,7 +2896,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>178</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>76</v>
@@ -4674,7 +4674,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>284</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>76</v>
@@ -4787,7 +4787,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>292</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>76</v>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:27+00:00</t>
+    <t>2026-06-18T08:56:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:56:30+00:00</t>
+    <t>2026-06-18T10:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:39:29+00:00</t>
+    <t>2026-06-18T11:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:30:08+00:00</t>
+    <t>2026-06-23T16:45:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -901,7 +901,7 @@
     <t>Goal.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition)
+    <t xml:space="preserve">Reference(https://bih-cei.de/fhir/therapieziele-onkologie/StructureDefinition/onko-condition)
 </t>
   </si>
   <si>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:45:59+00:00</t>
+    <t>2026-06-24T07:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$36</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="318">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:38:46+00:00</t>
+    <t>2026-06-25T15:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -482,6 +482,54 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>Goal.extension:acceptance</t>
+  </si>
+  <si>
+    <t>acceptance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {goal-acceptance}
+</t>
+  </si>
+  <si>
+    <t>Individual acceptance of goal</t>
+  </si>
+  <si>
+    <t>Information about the acceptance and relative priority assigned to the goal by the patient, practitioners and other stake-holders. In R6, this acceptance extension was elevated to the base Goal resource.</t>
+  </si>
+  <si>
+    <t>Goal.extension:reasonRejected</t>
+  </si>
+  <si>
+    <t>reasonRejected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {goal-reasonRejected}
+</t>
+  </si>
+  <si>
+    <t>The reason the goal was not accepted</t>
+  </si>
+  <si>
+    <t>The reason the goal was not accepted. Applies only if the status of the goal is rejected.</t>
+  </si>
+  <si>
+    <t>Goal.extension:relatedGoal</t>
+  </si>
+  <si>
+    <t>relatedGoal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {goal-relationship}
+</t>
+  </si>
+  <si>
+    <t>Goals related to this Goal</t>
+  </si>
+  <si>
+    <t>Establishes a relationship between this goal and other goals.</t>
   </si>
   <si>
     <t>Goal.modifierExtension</t>
@@ -1293,12 +1341,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="24.52734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.453125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.52734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.66796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.15625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2448,16 +2496,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2467,29 +2517,25 @@
         <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="O11" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
       </c>
@@ -2537,7 +2583,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2546,7 +2592,7 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>138</v>
@@ -2555,20 +2601,22 @@
         <v>76</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>76</v>
       </c>
@@ -2577,10 +2625,10 @@
         <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>76</v>
@@ -2589,20 +2637,16 @@
         <v>76</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>76</v>
       </c>
@@ -2650,7 +2694,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2659,63 +2703,61 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>164</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>76</v>
       </c>
@@ -2739,13 +2781,13 @@
         <v>76</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>76</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>76</v>
@@ -2763,68 +2805,72 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
+      <c r="A14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="AG13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="B14" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
       </c>
@@ -2848,13 +2894,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -2872,25 +2918,25 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>130</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>76</v>
@@ -2898,10 +2944,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2909,7 +2955,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>78</v>
@@ -2921,20 +2967,22 @@
         <v>76</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2959,11 +3007,13 @@
         <v>76</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>76</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>76</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>76</v>
@@ -2981,7 +3031,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2999,18 +3049,18 @@
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>76</v>
+        <v>173</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3018,7 +3068,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>87</v>
@@ -3027,25 +3077,25 @@
         <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -3070,13 +3120,13 @@
         <v>76</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>76</v>
@@ -3094,10 +3144,10 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>87</v>
@@ -3109,21 +3159,21 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>76</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3131,7 +3181,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>87</v>
@@ -3146,20 +3196,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>198</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>76</v>
       </c>
@@ -3183,13 +3229,13 @@
         <v>76</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>76</v>
@@ -3207,10 +3253,10 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>87</v>
@@ -3222,21 +3268,21 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>202</v>
+        <v>76</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3247,10 +3293,10 @@
         <v>87</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>76</v>
@@ -3259,17 +3305,17 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3294,13 +3340,11 @@
         <v>76</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>76</v>
@@ -3318,13 +3362,13 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>76</v>
@@ -3333,21 +3377,21 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>210</v>
+        <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>76</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3370,17 +3414,19 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="O19" t="s" s="2">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -3405,13 +3451,13 @@
         <v>76</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>199</v>
+        <v>111</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>76</v>
@@ -3429,7 +3475,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3447,18 +3493,18 @@
         <v>76</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>76</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3466,10 +3512,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>88</v>
@@ -3478,22 +3524,22 @@
         <v>76</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -3518,13 +3564,13 @@
         <v>76</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>76</v>
+        <v>216</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>76</v>
@@ -3542,36 +3588,36 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>228</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>76</v>
+        <v>218</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3579,31 +3625,33 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>76</v>
       </c>
@@ -3651,10 +3699,10 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>87</v>
@@ -3663,58 +3711,58 @@
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>76</v>
+        <v>225</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>132</v>
+        <v>229</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O22" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
       </c>
@@ -3738,13 +3786,13 @@
         <v>76</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>76</v>
+        <v>233</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>76</v>
@@ -3762,40 +3810,40 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="23" hidden="true">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>240</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3805,28 +3853,28 @@
         <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3875,7 +3923,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3884,22 +3932,22 @@
         <v>78</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>138</v>
+        <v>243</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>244</v>
       </c>
@@ -3918,22 +3966,22 @@
         <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>172</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3960,31 +4008,31 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>247</v>
+        <v>76</v>
       </c>
       <c r="Z24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3993,50 +4041,50 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>76</v>
+        <v>249</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>251</v>
@@ -4045,7 +4093,7 @@
         <v>252</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>253</v>
+        <v>164</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4071,93 +4119,95 @@
         <v>76</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="Y25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>76</v>
+        <v>255</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I26" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N26" s="2"/>
+      <c r="N26" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -4206,36 +4256,36 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4249,7 +4299,7 @@
         <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>76</v>
@@ -4258,17 +4308,15 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4293,13 +4341,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>76</v>
+        <v>262</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4317,7 +4365,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4326,7 +4374,7 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
@@ -4338,15 +4386,15 @@
         <v>76</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4360,25 +4408,25 @@
         <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>230</v>
+        <v>265</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4404,10 +4452,10 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>76</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>76</v>
@@ -4428,7 +4476,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4437,7 +4485,7 @@
         <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>76</v>
+        <v>242</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
@@ -4454,10 +4502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4480,18 +4528,18 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
@@ -4539,7 +4587,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4560,15 +4608,15 @@
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
         <v>276</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4579,30 +4627,30 @@
         <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>76</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N30" s="2"/>
-      <c r="O30" t="s" s="2">
-        <v>281</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>76</v>
       </c>
@@ -4650,13 +4698,13 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>76</v>
@@ -4668,18 +4716,18 @@
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4690,7 +4738,7 @@
         <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>76</v>
@@ -4702,20 +4750,18 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>289</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
       </c>
@@ -4763,13 +4809,13 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>76</v>
@@ -4778,21 +4824,21 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>76</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4803,32 +4849,30 @@
         <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
       </c>
@@ -4852,13 +4896,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>199</v>
+        <v>76</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -4876,13 +4920,13 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>76</v>
@@ -4897,15 +4941,15 @@
         <v>76</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>76</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4928,17 +4972,15 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
         <v>296</v>
       </c>
@@ -4989,7 +5031,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5007,14 +5049,353 @@
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>76</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM33">
+  <autoFilter ref="A1:AM36">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5024,7 +5405,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI32">
+  <conditionalFormatting sqref="A2:AI35">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:26:12+00:00</t>
+    <t>2026-07-20T12:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$38</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="328">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -474,10 +474,10 @@
 </t>
   </si>
   <si>
-    <t>Onkologische Therapieintention (Extension)</t>
-  </si>
-  <si>
-    <t>Strukturierte Codierung der Therapieintention (kurativ, neoadjuvant, adjuvant, Erhaltung, palliativ, supportiv). Verwendet in OnkoCarePlan und OnkoTherapyLine. Konzeptionell anschlussfähig an mCODE `procedure-intent`.</t>
+    <t>Therapieintention</t>
+  </si>
+  <si>
+    <t>Strukturierte Therapieintention – Hauptintention und optionale Behandlungsphase.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -494,10 +494,10 @@
 </t>
   </si>
   <si>
-    <t>Individual acceptance of goal</t>
-  </si>
-  <si>
-    <t>Information about the acceptance and relative priority assigned to the goal by the patient, practitioners and other stake-holders. In R6, this acceptance extension was elevated to the base Goal resource.</t>
+    <t>Zielakzeptanz</t>
+  </si>
+  <si>
+    <t>Akzeptanz und relative Priorität des Ziels durch Patient und Behandler – MCC goal-acceptance.</t>
   </si>
   <si>
     <t>Goal.extension:reasonRejected</t>
@@ -510,10 +510,10 @@
 </t>
   </si>
   <si>
-    <t>The reason the goal was not accepted</t>
-  </si>
-  <si>
-    <t>The reason the goal was not accepted. Applies only if the status of the goal is rejected.</t>
+    <t>Ablehnungsgrund</t>
+  </si>
+  <si>
+    <t>Begründung, warum das Ziel nicht akzeptiert bzw. abgelehnt wurde.</t>
   </si>
   <si>
     <t>Goal.extension:relatedGoal</t>
@@ -526,10 +526,10 @@
 </t>
   </si>
   <si>
-    <t>Goals related to this Goal</t>
-  </si>
-  <si>
-    <t>Establishes a relationship between this goal and other goals.</t>
+    <t>Zielbeziehung</t>
+  </si>
+  <si>
+    <t>Beziehung zu anderen Zielen – predecessor, successor, replacement, milestone.</t>
   </si>
   <si>
     <t>Goal.modifierExtension</t>
@@ -583,10 +583,10 @@
     <t>Goal.lifecycleStatus</t>
   </si>
   <si>
-    <t>proposed | planned | accepted | active | on-hold | completed | cancelled | entered-in-error | rejected</t>
-  </si>
-  <si>
-    <t>The state of the goal throughout its lifecycle.</t>
+    <t>Lebenszyklus-Status</t>
+  </si>
+  <si>
+    <t>Status des Ziels im Lebenszyklus, z. B. proposed, active, completed, rejected.</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the lifecycleStatus contains codes that mark the resource as not currently valid.</t>
@@ -620,10 +620,10 @@
 </t>
   </si>
   <si>
-    <t>in-progress | improving | worsening | no-change | achieved | sustaining | not-achieved | no-progress | not-attainable</t>
-  </si>
-  <si>
-    <t>Describes the progression, or lack thereof, towards the goal against the target.</t>
+    <t>Erreichungsgrad</t>
+  </si>
+  <si>
+    <t>Grad der Zielerreichung, z. B. erreicht, in Bearbeitung, nicht erreicht.</t>
   </si>
   <si>
     <t>Indicates the progression, or lack thereof, towards the goal against the target.</t>
@@ -638,10 +638,10 @@
     <t>Goal.category</t>
   </si>
   <si>
-    <t>E.g. Treatment, dietary, behavioral, etc.</t>
-  </si>
-  <si>
-    <t>Indicates a category the goal falls within.</t>
+    <t>Zielart</t>
+  </si>
+  <si>
+    <t>Art des onkologischen Therapieziels – Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme.</t>
   </si>
   <si>
     <t>Allows goals to be filtered and sorted.</t>
@@ -659,10 +659,10 @@
     <t>Goal.priority</t>
   </si>
   <si>
-    <t>high-priority | medium-priority | low-priority</t>
-  </si>
-  <si>
-    <t>Identifies the mutually agreed level of importance associated with reaching/sustaining the goal.</t>
+    <t>Priorität</t>
+  </si>
+  <si>
+    <t>Relative Priorität des Ziels bei mehreren konkurrierenden Zielen.</t>
   </si>
   <si>
     <t>Extensions are available to track priorities as established by each participant (i.e. Priority from the patient's perspective, different practitioners' perspectives, family member's perspectives)@@ -688,10 +688,10 @@
     <t>Goal.description</t>
   </si>
   <si>
-    <t>Code or text describing goal</t>
-  </si>
-  <si>
-    <t>Human-readable and/or coded description of a specific desired objective of care, such as "control blood pressure" or "negotiate an obstacle course" or "dance with child at wedding".</t>
+    <t>Zielbeschreibung</t>
+  </si>
+  <si>
+    <t>Klartext-Beschreibung des angestrebten Ziels.</t>
   </si>
   <si>
     <t>If no code is available, use CodeableConcept.text.</t>
@@ -725,10 +725,10 @@
 </t>
   </si>
   <si>
-    <t>Who this goal is intended for</t>
-  </si>
-  <si>
-    <t>Identifies the patient, group or organization for whom the goal is being established.</t>
+    <t>Patientin/Patient</t>
+  </si>
+  <si>
+    <t>Person, für die das Therapieziel gilt.</t>
   </si>
   <si>
     <t>Subject is optional to support annonymized reporting.</t>
@@ -750,10 +750,10 @@
 CodeableConcept</t>
   </si>
   <si>
-    <t>When goal pursuit begins</t>
-  </si>
-  <si>
-    <t>The date or event after which the goal should begin being pursued.</t>
+    <t>Zielbeginn</t>
+  </si>
+  <si>
+    <t>Beginn des angestrebten Ziels als Datum oder codiertes Ereignis.</t>
   </si>
   <si>
     <t>Goals can be established prior to there being an intention to start pursuing them; e.g. Goals for post-surgical recovery established prior to surgery.</t>
@@ -765,7 +765,42 @@
     <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>FiveWs.planned</t>
+  </si>
+  <si>
+    <t>Goal.start[x]:startDate</t>
+  </si>
+  <si>
+    <t>startDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>Zielbeginn als Datum</t>
+  </si>
+  <si>
+    <t>Beginn des Ziels als Datum.</t>
+  </si>
+  <si>
+    <t>Goal.start[x]:startCodeableConcept</t>
+  </si>
+  <si>
+    <t>startCodeableConcept</t>
+  </si>
+  <si>
+    <t>Zielbeginn als Code</t>
+  </si>
+  <si>
+    <t>Beginn des Ziels als codiertes Ereignis.</t>
   </si>
   <si>
     <t>Goal.target</t>
@@ -775,10 +810,10 @@
 </t>
   </si>
   <si>
-    <t>Target outcome for the goal</t>
-  </si>
-  <si>
-    <t>Indicates what should be done by when.</t>
+    <t>Zielwert</t>
+  </si>
+  <si>
+    <t>Angestrebter messbarer Zielzustand.</t>
   </si>
   <si>
     <t>When multiple targets are present for a single goal instance, all targets must be met for the overall goal to be met.</t>
@@ -846,10 +881,10 @@
     <t>Goal.target.measure</t>
   </si>
   <si>
-    <t>The parameter whose value is being tracked</t>
-  </si>
-  <si>
-    <t>The parameter whose value is being tracked, e.g. body weight, blood pressure, or hemoglobin A1c level.</t>
+    <t>Zielparameter</t>
+  </si>
+  <si>
+    <t>Parameter bzw. Messgröße, an der die Zielerreichung gemessen wird.</t>
   </si>
   <si>
     <t>Codes to identify the value being tracked, e.g. body weight, blood pressure, or hemoglobin A1c level.</t>
@@ -865,10 +900,10 @@
 RangeCodeableConceptstringbooleanintegerRatio</t>
   </si>
   <si>
-    <t>The target value to be achieved</t>
-  </si>
-  <si>
-    <t>The target value of the focus to be achieved to signify the fulfillment of the goal, e.g. 150 pounds, 7.0%. Either the high or low or both values of the range can be specified. When a low value is missing, it indicates that the goal is achieved at any focus value at or below the high value. Similarly, if the high value is missing, it indicates that the goal is achieved at any focus value at or above the low value.</t>
+    <t>Zielwert-Ausprägung</t>
+  </si>
+  <si>
+    <t>Angestrebter Wert bzw. Wertebereich des Zielparameters.</t>
   </si>
   <si>
     <t>A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Goal.target.measure defines a coded value.</t>
@@ -884,10 +919,10 @@
 Duration</t>
   </si>
   <si>
-    <t>Reach goal on or before</t>
-  </si>
-  <si>
-    <t>Indicates either the date or the duration after start by which the goal should be met.</t>
+    <t>Zieltermin</t>
+  </si>
+  <si>
+    <t>Zeitpunkt bzw. Frist, bis zu der das Ziel erreicht werden soll.</t>
   </si>
   <si>
     <t>Identifies when the goal should be evaluated.</t>
@@ -897,10 +932,6 @@
   </si>
   <si>
     <t>Goal.statusDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date
-</t>
   </si>
   <si>
     <t>When goal status took effect</t>
@@ -934,10 +965,10 @@
 </t>
   </si>
   <si>
-    <t>Who's responsible for creating Goal?</t>
-  </si>
-  <si>
-    <t>Indicates whose goal this is - patient goal, practitioner goal, etc.</t>
+    <t>Verfasser</t>
+  </si>
+  <si>
+    <t>Person, die das Ziel formuliert hat – Behandler oder Patient.</t>
   </si>
   <si>
     <t>This is the individual responsible for establishing the goal, not necessarily who recorded it.  (For that, use the Provenance resource.).</t>
@@ -953,10 +984,10 @@
 </t>
   </si>
   <si>
-    <t>Issues addressed by this goal</t>
-  </si>
-  <si>
-    <t>The identified conditions and other health record elements that are intended to be addressed by the goal.</t>
+    <t>Adressierte Erkrankung</t>
+  </si>
+  <si>
+    <t>Referenz auf die adressierte Tumorerkrankung OnkoCondition.</t>
   </si>
   <si>
     <t>Allows specific goals to explicitly linked to the concerns they're dealing with - makes the goal more understandable.</t>
@@ -975,10 +1006,10 @@
 </t>
   </si>
   <si>
-    <t>Comments about the goal</t>
-  </si>
-  <si>
-    <t>Any comments related to the goal.</t>
+    <t>Hinweis</t>
+  </si>
+  <si>
+    <t>Ergänzende Anmerkungen zum Ziel.</t>
   </si>
   <si>
     <t>May be used for progress notes, concerns or other related information that doesn't actually describe the goal itself.</t>
@@ -996,10 +1027,10 @@
     <t>Goal.outcomeCode</t>
   </si>
   <si>
-    <t>What result was achieved regarding the goal?</t>
-  </si>
-  <si>
-    <t>Identifies the change (or lack of change) at the point when the status of the goal is assessed.</t>
+    <t>Ergebnis-Code</t>
+  </si>
+  <si>
+    <t>Codiertes Ergebnis der Zielverfolgung.</t>
   </si>
   <si>
     <t>Note that this should not duplicate the goal status.</t>
@@ -1018,10 +1049,10 @@
 </t>
   </si>
   <si>
-    <t>Observation that resulted from goal</t>
-  </si>
-  <si>
-    <t>Details of what's changed (or not changed).</t>
+    <t>Ergebnis-Referenz</t>
+  </si>
+  <si>
+    <t>Referenz auf Verlaufs-Observations, die das Tumoransprechen dokumentieren.</t>
   </si>
   <si>
     <t>The goal outcome is independent of the outcome of the related activities.  For example, if the Goal is to achieve a target body weight of 150 lb and a care plan activity is defined to diet, then the care plan’s activity outcome could be calories consumed whereas goal outcome is an observation for the actual body weight measured.</t>
@@ -1341,12 +1372,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM36"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="25.453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="28.87109375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.52734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.15625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.4453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3723,7 +3754,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>228</v>
       </c>
@@ -3798,16 +3829,14 @@
         <v>76</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>76</v>
+        <v>236</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>228</v>
@@ -3831,17 +3860,19 @@
         <v>76</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>76</v>
       </c>
@@ -3850,7 +3881,7 @@
         <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>88</v>
@@ -3859,22 +3890,20 @@
         <v>76</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>76</v>
@@ -3923,38 +3952,40 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AK23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" hidden="true">
-      <c r="A24" t="s" s="2">
+      <c r="B24" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="B24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>76</v>
       </c>
@@ -3966,25 +3997,27 @@
         <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M24" t="s" s="2">
-        <v>247</v>
-      </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
       </c>
@@ -4008,13 +4041,13 @@
         <v>76</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>76</v>
+        <v>233</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>76</v>
+        <v>234</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>76</v>
@@ -4032,7 +4065,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4044,28 +4077,28 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="25" hidden="true">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4075,7 +4108,7 @@
         <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>76</v>
@@ -4084,18 +4117,20 @@
         <v>76</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>132</v>
+        <v>248</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>76</v>
       </c>
@@ -4143,7 +4178,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4152,16 +4187,16 @@
         <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>249</v>
+        <v>76</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>76</v>
@@ -4169,46 +4204,42 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>255</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
       </c>
@@ -4256,67 +4287,69 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>76</v>
+        <v>161</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4341,13 +4374,13 @@
         <v>76</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>262</v>
+        <v>76</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>76</v>
@@ -4365,70 +4398,72 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>76</v>
+        <v>266</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I28" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="J28" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>265</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>76</v>
       </c>
@@ -4452,49 +4487,49 @@
         <v>76</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>242</v>
+        <v>76</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>76</v>
@@ -4528,18 +4563,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M29" t="s" s="2">
-        <v>273</v>
-      </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>274</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
       </c>
@@ -4563,13 +4596,13 @@
         <v>76</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>76</v>
+        <v>273</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>76</v>
+        <v>274</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>76</v>
@@ -4596,7 +4629,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4608,15 +4641,15 @@
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
         <v>275</v>
       </c>
-    </row>
-    <row r="30" hidden="true">
-      <c r="A30" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4630,7 +4663,7 @@
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>76</v>
@@ -4639,16 +4672,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4674,10 +4707,10 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>76</v>
+        <v>214</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>76</v>
+        <v>280</v>
       </c>
       <c r="Z30" t="s" s="2">
         <v>76</v>
@@ -4698,7 +4731,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4707,7 +4740,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>253</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -4719,15 +4752,15 @@
         <v>76</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
         <v>281</v>
       </c>
-    </row>
-    <row r="31" hidden="true">
-      <c r="A31" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4741,16 +4774,16 @@
         <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>245</v>
+        <v>282</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>283</v>
@@ -4758,10 +4791,10 @@
       <c r="M31" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="N31" s="2"/>
+      <c r="O31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
       </c>
@@ -4809,7 +4842,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4830,15 +4863,15 @@
         <v>76</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4852,7 +4885,7 @@
         <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>76</v>
@@ -4861,7 +4894,7 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>287</v>
+        <v>240</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>288</v>
@@ -4920,7 +4953,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4944,7 +4977,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>292</v>
       </c>
@@ -4960,10 +4993,10 @@
         <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>76</v>
@@ -4972,18 +5005,18 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>296</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>76</v>
       </c>
@@ -5037,7 +5070,7 @@
         <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>76</v>
@@ -5049,18 +5082,18 @@
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>297</v>
+        <v>76</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5071,32 +5104,30 @@
         <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L34" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
       </c>
@@ -5144,13 +5175,13 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>76</v>
@@ -5159,21 +5190,21 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>76</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>76</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5187,7 +5218,7 @@
         <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>76</v>
@@ -5196,19 +5227,17 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>187</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>310</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -5233,13 +5262,13 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>214</v>
+        <v>76</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>312</v>
+        <v>76</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>76</v>
@@ -5257,7 +5286,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5275,18 +5304,18 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>76</v>
+        <v>307</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5300,7 +5329,7 @@
         <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>76</v>
@@ -5309,19 +5338,19 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>76</v>
@@ -5370,7 +5399,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5385,17 +5414,243 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>76</v>
+        <v>315</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>76</v>
+        <v>316</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>76</v>
       </c>
     </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM36">
+  <autoFilter ref="A1:AM38">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5405,7 +5660,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI35">
+  <conditionalFormatting sqref="A2:AI37">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -92,7 +92,7 @@
 Ergebnissen (Verlaufs-Observations) verknüpft wird.
 Onkologiespezifische Ergänzungen gegenüber MCC:
 - Die Zielart wird über `category` aus `OnkoTherapyGoalTypeVS` codiert (Heilung,
-  Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme).
+  Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt).
 - Über die Extension `onko-therapy-intent` kann zusätzlich die Therapieintention der
   zugehörigen Behandlungslinie hinterlegt werden.
 - `outcomeReference` bindet das Ziel an Verlaufs-Observations (z. B. mCODE
@@ -641,7 +641,7 @@
     <t>Zielart</t>
   </si>
   <si>
-    <t>Art des onkologischen Therapieziels – Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt, Studienteilnahme.</t>
+    <t>Art des onkologischen Therapieziels – Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt.</t>
   </si>
   <si>
     <t>Allows goals to be filtered and sorted.</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3308,7 +3308,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>193</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>76</v>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-onko-therapy-goal.xlsx
+++ b/ci-build/StructureDefinition-onko-therapy-goal.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
